--- a/merged_orders/merged_跨7.xlsx
+++ b/merged_orders/merged_跨7.xlsx
@@ -429,17 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>下单件数</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SKU ID</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>产品名称</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -476,18 +476,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>洗护套装</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>1.731979052094821e+18</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>洗护套装</t>
+          <t>1731979052094821372</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -524,18 +526,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>洗护套装</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>1.731979052094821e+18</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>洗护套装</t>
+          <t>1731979052094821372</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -572,18 +576,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>洗发水买一送一</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" t="n">
-        <v>1.730926757262366e+18</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>洗发水买一送一</t>
+          <t>1730926757262365692</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,18 +626,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>洗发水精油</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>1.730891393980863e+18</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>洗发水精油</t>
+          <t>1730891393980863484</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -668,18 +676,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>精油一瓶</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>1.730891393980995e+18</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>精油一瓶</t>
+          <t>1730891393980994556</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -716,18 +726,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>精油一瓶</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>1.730891393980995e+18</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>精油一瓶</t>
+          <t>1730891393980994556</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -764,18 +776,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>洗发水</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>1.730845782743881e+18</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>洗发水</t>
+          <t>1730845782743880700</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -812,18 +826,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>洗护套装</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>1.731979052094821e+18</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>洗护套装</t>
+          <t>1731979052094821372</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -860,18 +876,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>洗发水</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>1.73197904451519e+18</v>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>洗发水</t>
+          <t>1731979044515189756</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -908,18 +926,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>洗护套装</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>1.731979052094821e+18</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>洗护套装</t>
+          <t>1731979052094821372</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -956,18 +976,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>洗发水</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>1.730845782743881e+18</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>洗发水</t>
+          <t>1730845782743880700</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1004,18 +1026,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>洗发水</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>1.730845782743881e+18</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>洗发水</t>
+          <t>1730845782743880700</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1052,18 +1076,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>洗发水</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>1.730845782743881e+18</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>洗发水</t>
+          <t>1730845782743880700</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1100,18 +1126,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>洗护套装</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>1.731979052094821e+18</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>洗护套装</t>
+          <t>1731979052094821372</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1148,18 +1176,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>洗发水</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>1.73197904451519e+18</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>洗发水</t>
+          <t>1731979044515189756</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1196,18 +1226,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>洗发水</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>1.730845782743881e+18</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>洗发水</t>
+          <t>1730845782743880700</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1244,18 +1276,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>洗发水</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>1.730845782743881e+18</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>洗发水</t>
+          <t>1730845782743880700</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
